--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteAbgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:21:25+00:00</t>
+    <t>2026-05-13T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteAbgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:40:49+00:00</t>
+    <t>2026-05-15T11:09:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteAbgabe.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$49</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AO$50</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1833" uniqueCount="386">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="392">
   <si>
     <t>Property</t>
   </si>
@@ -39,7 +39,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AtElgaEmedMedicationRequestDurchgefuehrteAbgabe</t>
+    <t>AtElgaEmedMedicationDispenseDurchgefuehrteAbgabe</t>
   </si>
   <si>
     <t>Title</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:09:11+00:00</t>
+    <t>2026-05-22T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -88,8 +88,8 @@
   </si>
   <si>
     <t>Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
-In der durchgeführten Abgabe können Abweichungen hinsichtlich der Dosierung des Medikaments dokumentiert werden.
-Sofern eine zugehörige geplante Abgabe vorliegt, muss diese referenziert werden. Einer mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige geplante Abgabe, ersichtlich.</t>
+In der durchgeführten Abgabe können Abweichungen hinsichtlich des Medikaments und dessen Dosierung dokumentiert werden.
+Sofern eine zugehörige geplante Abgabe vorliegt, muss diese referenziert werden. Eine mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige geplante Abgabe, ersichtlich.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -478,6 +478,26 @@
 </t>
   </si>
   <si>
+    <t>MedicationDispense.extension:recorded</t>
+  </si>
+  <si>
+    <t>recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.recorded}
+</t>
+  </si>
+  <si>
+    <t>Datum und Uhrzeit, zu denen die Abgabe erfasst wurde. Dies muss nicht unbedingt mit dem Zeitpunkt übereinstimmen, zu dem das Medikament dem Patienten ausgehändigt wurde (z.B. bei Nacherfassung der Abgabe).</t>
+  </si>
+  <si>
+    <t>R5: `MedicationDispense.recorded` (new:dateTime)</t>
+  </si>
+  <si>
+    <t>Element `MedicationDispense.recorded` has a context of MedicationDispense based on following the parent source element upwards and mapping to `MedicationDispense`.
+Element `MedicationDispense.recorded` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
+  </si>
+  <si>
     <t>MedicationDispense.modifierExtension</t>
   </si>
   <si>
@@ -508,7 +528,7 @@
 </t>
   </si>
   <si>
-    <t>Durchgeführte-Abgabe-ID.</t>
+    <t>Durchgeführte-Abgabe-ID. Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -1554,7 +1574,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AO49"/>
+  <dimension ref="A1:AO50"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="55.03515625" customWidth="true" bestFit="true"/>
@@ -2552,7 +2572,7 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G9" t="s" s="2">
         <v>80</v>
@@ -2776,43 +2796,43 @@
         <v>147</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>147</v>
-      </c>
-      <c r="C11" s="2"/>
+        <v>132</v>
+      </c>
+      <c r="C11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="D11" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O11" t="s" s="2">
         <v>152</v>
       </c>
+      <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>21</v>
       </c>
@@ -2860,7 +2880,7 @@
         <v>21</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>153</v>
+        <v>138</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>79</v>
@@ -2869,7 +2889,7 @@
         <v>80</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>21</v>
+        <v>146</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>139</v>
@@ -2878,7 +2898,7 @@
         <v>21</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>131</v>
+        <v>21</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>21</v>
@@ -2892,44 +2912,46 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
-        <v>21</v>
+        <v>154</v>
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I12" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J12" t="s" s="2">
         <v>21</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>155</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>156</v>
       </c>
-      <c r="M12" t="s" s="2">
+      <c r="N12" t="s" s="2">
         <v>157</v>
       </c>
-      <c r="N12" t="s" s="2">
+      <c r="O12" t="s" s="2">
         <v>158</v>
       </c>
-      <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>21</v>
       </c>
@@ -2977,7 +2999,7 @@
         <v>21</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>79</v>
@@ -2989,19 +3011,19 @@
         <v>21</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>21</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>131</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>21</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>21</v>
       </c>
       <c r="AO12" t="s" s="2">
         <v>21</v>
@@ -3009,10 +3031,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3035,15 +3057,17 @@
         <v>21</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M13" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="N13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="M13" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>21</v>
@@ -3092,7 +3116,7 @@
         <v>21</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>79</v>
@@ -3107,22 +3131,22 @@
         <v>100</v>
       </c>
       <c r="AK13" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AL13" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="AM13" t="s" s="2">
         <v>167</v>
       </c>
-      <c r="AL13" t="s" s="2">
+      <c r="AN13" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AM13" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN13" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AO13" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>169</v>
       </c>
@@ -3135,32 +3159,30 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I14" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" t="s" s="2">
         <v>172</v>
       </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>21</v>
@@ -3185,13 +3207,13 @@
         <v>21</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>173</v>
+        <v>21</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>174</v>
+        <v>21</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>175</v>
+        <v>21</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>21</v>
@@ -3212,10 +3234,10 @@
         <v>169</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>21</v>
@@ -3224,27 +3246,27 @@
         <v>100</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>178</v>
+        <v>21</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>179</v>
+        <v>21</v>
       </c>
       <c r="AO14" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3252,30 +3274,32 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G15" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>181</v>
+        <v>108</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>183</v>
-      </c>
-      <c r="N15" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="N15" t="s" s="2">
+        <v>178</v>
+      </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
         <v>21</v>
@@ -3300,32 +3324,34 @@
         <v>21</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>21</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>21</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>188</v>
+        <v>21</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH15" t="s" s="2">
         <v>88</v>
@@ -3337,31 +3363,29 @@
         <v>100</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>189</v>
+        <v>182</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>21</v>
+        <v>184</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c r="AO15" t="s" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>180</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>192</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>21</v>
       </c>
@@ -3373,7 +3397,7 @@
         <v>88</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>21</v>
@@ -3382,13 +3406,13 @@
         <v>21</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -3415,31 +3439,29 @@
         <v>21</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="Z16" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="AA16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB16" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AC16" s="2"/>
+      <c r="AD16" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE16" t="s" s="2">
+        <v>194</v>
+      </c>
+      <c r="AF16" t="s" s="2">
         <v>186</v>
-      </c>
-      <c r="AA16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE16" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF16" t="s" s="2">
-        <v>180</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -3454,10 +3476,10 @@
         <v>100</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>21</v>
@@ -3469,15 +3491,15 @@
         <v>21</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>21</v>
@@ -3487,10 +3509,10 @@
         <v>79</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>21</v>
@@ -3499,13 +3521,13 @@
         <v>21</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3532,13 +3554,13 @@
         <v>21</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>21</v>
@@ -3556,7 +3578,7 @@
         <v>21</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -3571,10 +3593,10 @@
         <v>100</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>21</v>
@@ -3588,12 +3610,14 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="C18" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="C18" t="s" s="2">
+        <v>201</v>
+      </c>
       <c r="D18" t="s" s="2">
         <v>21</v>
       </c>
@@ -3614,17 +3638,15 @@
         <v>21</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>181</v>
+        <v>202</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="N18" t="s" s="2">
-        <v>201</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="N18" s="2"/>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>21</v>
@@ -3649,13 +3671,13 @@
         <v>21</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>112</v>
+        <v>21</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>202</v>
+        <v>21</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>203</v>
+        <v>21</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>21</v>
@@ -3673,7 +3695,7 @@
         <v>21</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>79</v>
@@ -3688,27 +3710,27 @@
         <v>100</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>21</v>
+        <v>195</v>
       </c>
       <c r="AL18" t="s" s="2">
+        <v>196</v>
+      </c>
+      <c r="AM18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN18" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO18" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" hidden="true">
+      <c r="A19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="AM18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO18" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>205</v>
-      </c>
       <c r="B19" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3716,31 +3738,31 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J19" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>207</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>209</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3766,13 +3788,13 @@
         <v>21</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>21</v>
+        <v>112</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>21</v>
+        <v>208</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>21</v>
+        <v>209</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>21</v>
@@ -3790,10 +3812,10 @@
         <v>21</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH19" t="s" s="2">
         <v>88</v>
@@ -3805,27 +3827,27 @@
         <v>100</v>
       </c>
       <c r="AK19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL19" t="s" s="2">
         <v>210</v>
       </c>
-      <c r="AL19" t="s" s="2">
-        <v>211</v>
-      </c>
       <c r="AM19" t="s" s="2">
-        <v>212</v>
+        <v>21</v>
       </c>
       <c r="AN19" t="s" s="2">
-        <v>213</v>
+        <v>21</v>
       </c>
       <c r="AO19" t="s" s="2">
-        <v>214</v>
+        <v>21</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3848,16 +3870,16 @@
         <v>89</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3907,10 +3929,10 @@
         <v>21</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>88</v>
@@ -3922,27 +3944,27 @@
         <v>100</v>
       </c>
       <c r="AK20" t="s" s="2">
+        <v>216</v>
+      </c>
+      <c r="AL20" t="s" s="2">
+        <v>217</v>
+      </c>
+      <c r="AM20" t="s" s="2">
+        <v>218</v>
+      </c>
+      <c r="AN20" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AO20" t="s" s="2">
         <v>220</v>
       </c>
-      <c r="AL20" t="s" s="2">
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="2">
         <v>221</v>
       </c>
-      <c r="AM20" t="s" s="2">
-        <v>222</v>
-      </c>
-      <c r="AN20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO20" t="s" s="2">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="21" hidden="true">
-      <c r="A21" t="s" s="2">
-        <v>224</v>
-      </c>
       <c r="B21" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3950,30 +3972,32 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>21</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K21" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="L21" t="s" s="2">
+        <v>223</v>
+      </c>
+      <c r="M21" t="s" s="2">
+        <v>224</v>
+      </c>
+      <c r="N21" t="s" s="2">
         <v>225</v>
       </c>
-      <c r="L21" t="s" s="2">
-        <v>226</v>
-      </c>
-      <c r="M21" t="s" s="2">
-        <v>227</v>
-      </c>
-      <c r="N21" s="2"/>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>21</v>
@@ -4022,7 +4046,7 @@
         <v>21</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -4037,19 +4061,19 @@
         <v>100</v>
       </c>
       <c r="AK21" t="s" s="2">
+        <v>226</v>
+      </c>
+      <c r="AL21" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AM21" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="AL21" t="s" s="2">
+      <c r="AN21" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO21" t="s" s="2">
         <v>229</v>
-      </c>
-      <c r="AM21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN21" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO21" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="22" hidden="true">
@@ -4143,7 +4167,7 @@
         <v>79</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>21</v>
@@ -4152,13 +4176,13 @@
         <v>100</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>21</v>
+        <v>234</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>235</v>
+        <v>21</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>21</v>
@@ -4167,7 +4191,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>236</v>
       </c>
@@ -4180,13 +4204,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>21</v>
@@ -4267,14 +4291,14 @@
         <v>100</v>
       </c>
       <c r="AK23" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL23" t="s" s="2">
         <v>240</v>
       </c>
-      <c r="AL23" t="s" s="2">
+      <c r="AM23" t="s" s="2">
         <v>241</v>
       </c>
-      <c r="AM23" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AN23" t="s" s="2">
         <v>21</v>
       </c>
@@ -4282,7 +4306,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
         <v>242</v>
       </c>
@@ -4295,13 +4319,13 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G24" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>21</v>
@@ -4367,22 +4391,22 @@
         <v>21</v>
       </c>
       <c r="AF24" t="s" s="2">
+        <v>242</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK24" t="s" s="2">
         <v>246</v>
-      </c>
-      <c r="AG24" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH24" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AJ24" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AK24" t="s" s="2">
-        <v>21</v>
       </c>
       <c r="AL24" t="s" s="2">
         <v>247</v>
@@ -4406,14 +4430,14 @@
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H25" t="s" s="2">
         <v>21</v>
@@ -4425,17 +4449,15 @@
         <v>21</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>133</v>
+        <v>249</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>21</v>
@@ -4484,25 +4506,25 @@
         <v>21</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>21</v>
@@ -4516,14 +4538,14 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
-        <v>253</v>
+        <v>154</v>
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
@@ -4536,26 +4558,24 @@
         <v>21</v>
       </c>
       <c r="I26" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K26" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O26" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>21</v>
       </c>
@@ -4603,7 +4623,7 @@
         <v>21</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>79</v>
@@ -4621,7 +4641,7 @@
         <v>21</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>131</v>
+        <v>253</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>21</v>
@@ -4635,43 +4655,45 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I27" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>181</v>
+        <v>133</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>259</v>
-      </c>
-      <c r="N27" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N27" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="O27" t="s" s="2">
-        <v>260</v>
+        <v>158</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>21</v>
@@ -4696,66 +4718,66 @@
         <v>21</v>
       </c>
       <c r="X27" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y27" t="s" s="2">
-        <v>261</v>
+        <v>21</v>
       </c>
       <c r="Z27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF27" t="s" s="2">
         <v>262</v>
       </c>
-      <c r="AA27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF27" t="s" s="2">
-        <v>257</v>
-      </c>
       <c r="AG27" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL27" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AM27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN27" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO27" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" hidden="true">
+      <c r="A28" t="s" s="2">
         <v>263</v>
       </c>
-      <c r="AM27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN27" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO27" t="s" s="2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="s" s="2">
-        <v>264</v>
-      </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4763,13 +4785,13 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I28" t="s" s="2">
         <v>21</v>
@@ -4778,16 +4800,18 @@
         <v>21</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>264</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>265</v>
       </c>
-      <c r="L28" t="s" s="2">
+      <c r="N28" s="2"/>
+      <c r="O28" t="s" s="2">
         <v>266</v>
       </c>
-      <c r="M28" t="s" s="2">
-        <v>267</v>
-      </c>
-      <c r="N28" s="2"/>
-      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>21</v>
       </c>
@@ -4811,13 +4835,13 @@
         <v>21</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>21</v>
+        <v>267</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>21</v>
+        <v>268</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>21</v>
@@ -4835,10 +4859,10 @@
         <v>21</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH28" t="s" s="2">
         <v>88</v>
@@ -4850,7 +4874,7 @@
         <v>100</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>268</v>
+        <v>21</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>269</v>
@@ -4865,7 +4889,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="29" hidden="true">
+    <row r="29">
       <c r="A29" t="s" s="2">
         <v>270</v>
       </c>
@@ -4878,13 +4902,13 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H29" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I29" t="s" s="2">
         <v>21</v>
@@ -4953,7 +4977,7 @@
         <v>270</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>88</v>
@@ -4965,10 +4989,10 @@
         <v>100</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>21</v>
+        <v>274</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>21</v>
@@ -4980,12 +5004,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4996,10 +5020,10 @@
         <v>79</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>21</v>
@@ -5008,17 +5032,15 @@
         <v>21</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N30" t="s" s="2">
         <v>279</v>
       </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>21</v>
@@ -5067,13 +5089,13 @@
         <v>21</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>21</v>
@@ -5082,27 +5104,27 @@
         <v>100</v>
       </c>
       <c r="AK30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL30" t="s" s="2">
         <v>280</v>
       </c>
-      <c r="AL30" t="s" s="2">
-        <v>281</v>
-      </c>
       <c r="AM30" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>282</v>
+        <v>21</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>283</v>
+        <v>21</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5110,7 +5132,7 @@
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
         <v>88</v>
@@ -5125,15 +5147,17 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>181</v>
+        <v>282</v>
       </c>
       <c r="L31" t="s" s="2">
+        <v>283</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>284</v>
+      </c>
+      <c r="N31" t="s" s="2">
         <v>285</v>
       </c>
-      <c r="M31" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>21</v>
@@ -5158,13 +5182,13 @@
         <v>21</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>286</v>
+        <v>21</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>287</v>
+        <v>21</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>21</v>
@@ -5182,13 +5206,13 @@
         <v>21</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>21</v>
@@ -5197,27 +5221,27 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>21</v>
+        <v>286</v>
       </c>
       <c r="AL31" t="s" s="2">
+        <v>287</v>
+      </c>
+      <c r="AM31" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN31" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AM31" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN31" t="s" s="2">
+      <c r="AO31" t="s" s="2">
         <v>289</v>
-      </c>
-      <c r="AO31" t="s" s="2">
-        <v>290</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5240,13 +5264,13 @@
         <v>21</v>
       </c>
       <c r="K32" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>291</v>
+      </c>
+      <c r="M32" t="s" s="2">
         <v>292</v>
-      </c>
-      <c r="L32" t="s" s="2">
-        <v>293</v>
-      </c>
-      <c r="M32" t="s" s="2">
-        <v>294</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5273,13 +5297,13 @@
         <v>21</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>21</v>
+        <v>292</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>21</v>
+        <v>293</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5297,7 +5321,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5315,24 +5339,24 @@
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AM32" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN32" t="s" s="2">
         <v>295</v>
       </c>
-      <c r="AM32" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN32" t="s" s="2">
+      <c r="AO32" t="s" s="2">
         <v>296</v>
       </c>
-      <c r="AO32" t="s" s="2">
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
         <v>297</v>
       </c>
-    </row>
-    <row r="33" hidden="true">
-      <c r="A33" t="s" s="2">
-        <v>298</v>
-      </c>
       <c r="B33" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5340,13 +5364,13 @@
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>21</v>
@@ -5355,7 +5379,7 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="L33" t="s" s="2">
         <v>299</v>
@@ -5412,7 +5436,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5436,18 +5460,18 @@
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>21</v>
+        <v>302</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5467,10 +5491,10 @@
         <v>21</v>
       </c>
       <c r="J34" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="L34" t="s" s="2">
         <v>305</v>
@@ -5527,7 +5551,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5551,18 +5575,18 @@
         <v>21</v>
       </c>
       <c r="AN34" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO34" t="s" s="2">
         <v>308</v>
       </c>
-      <c r="AO34" t="s" s="2">
+    </row>
+    <row r="35" hidden="true">
+      <c r="A35" t="s" s="2">
         <v>309</v>
       </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="s" s="2">
-        <v>310</v>
-      </c>
       <c r="B35" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5570,22 +5594,22 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J35" t="s" s="2">
         <v>89</v>
       </c>
-      <c r="I35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="J35" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="K35" t="s" s="2">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="L35" t="s" s="2">
         <v>311</v>
@@ -5642,7 +5666,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5657,27 +5681,27 @@
         <v>100</v>
       </c>
       <c r="AK35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL35" t="s" s="2">
         <v>313</v>
       </c>
-      <c r="AL35" t="s" s="2">
+      <c r="AM35" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN35" t="s" s="2">
         <v>314</v>
       </c>
-      <c r="AM35" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN35" t="s" s="2">
-        <v>308</v>
-      </c>
       <c r="AO35" t="s" s="2">
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
-    <row r="36" hidden="true">
+    <row r="36">
       <c r="A36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5685,13 +5709,13 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>21</v>
@@ -5700,13 +5724,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>271</v>
+        <v>310</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5757,7 +5781,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5772,19 +5796,19 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>21</v>
+        <v>319</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>320</v>
+        <v>315</v>
       </c>
     </row>
     <row r="37" hidden="true">
@@ -5815,13 +5839,13 @@
         <v>21</v>
       </c>
       <c r="K37" t="s" s="2">
+        <v>277</v>
+      </c>
+      <c r="L37" t="s" s="2">
         <v>322</v>
       </c>
-      <c r="L37" t="s" s="2">
+      <c r="M37" t="s" s="2">
         <v>323</v>
-      </c>
-      <c r="M37" t="s" s="2">
-        <v>324</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5878,7 +5902,7 @@
         <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI37" t="s" s="2">
         <v>21</v>
@@ -5890,19 +5914,19 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
+        <v>324</v>
+      </c>
+      <c r="AM37" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN37" t="s" s="2">
         <v>325</v>
       </c>
-      <c r="AM37" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN37" t="s" s="2">
+      <c r="AO37" t="s" s="2">
         <v>326</v>
       </c>
-      <c r="AO37" t="s" s="2">
-        <v>21</v>
-      </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>327</v>
       </c>
@@ -5918,10 +5942,10 @@
         <v>79</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="I38" t="s" s="2">
         <v>21</v>
@@ -6002,27 +6026,27 @@
         <v>100</v>
       </c>
       <c r="AK38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL38" t="s" s="2">
         <v>331</v>
       </c>
-      <c r="AL38" t="s" s="2">
+      <c r="AM38" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN38" t="s" s="2">
         <v>332</v>
       </c>
-      <c r="AM38" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN38" t="s" s="2">
-        <v>21</v>
-      </c>
       <c r="AO38" t="s" s="2">
-        <v>333</v>
+        <v>21</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6045,17 +6069,15 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="L39" t="s" s="2">
         <v>335</v>
       </c>
-      <c r="L39" t="s" s="2">
+      <c r="M39" t="s" s="2">
         <v>336</v>
       </c>
-      <c r="M39" t="s" s="2">
-        <v>337</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>338</v>
-      </c>
+      <c r="N39" s="2"/>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>21</v>
@@ -6104,7 +6126,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6119,22 +6141,22 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>21</v>
+        <v>337</v>
       </c>
       <c r="AL39" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="AM39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN39" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO39" t="s" s="2">
         <v>339</v>
       </c>
-      <c r="AM39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AO39" t="s" s="2">
-        <v>21</v>
-      </c>
     </row>
-    <row r="40" hidden="true">
+    <row r="40">
       <c r="A40" t="s" s="2">
         <v>340</v>
       </c>
@@ -6150,10 +6172,10 @@
         <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H40" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="I40" t="s" s="2">
         <v>21</v>
@@ -6162,15 +6184,17 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>237</v>
+        <v>341</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N40" s="2"/>
+        <v>343</v>
+      </c>
+      <c r="N40" t="s" s="2">
+        <v>344</v>
+      </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
         <v>21</v>
@@ -6225,7 +6249,7 @@
         <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>21</v>
@@ -6237,13 +6261,13 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>344</v>
+        <v>21</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>21</v>
@@ -6251,10 +6275,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6265,7 +6289,7 @@
         <v>79</v>
       </c>
       <c r="G41" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H41" t="s" s="2">
         <v>21</v>
@@ -6280,10 +6304,10 @@
         <v>243</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>244</v>
+        <v>347</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>245</v>
+        <v>348</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6334,7 +6358,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>246</v>
+        <v>346</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6346,19 +6370,19 @@
         <v>21</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>21</v>
+        <v>100</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>247</v>
+        <v>349</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>21</v>
+        <v>350</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6366,21 +6390,21 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
-        <v>148</v>
+        <v>21</v>
       </c>
       <c r="E42" s="2"/>
       <c r="F42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H42" t="s" s="2">
         <v>21</v>
@@ -6392,17 +6416,15 @@
         <v>21</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>133</v>
+        <v>249</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>250</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>251</v>
+      </c>
+      <c r="N42" s="2"/>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
         <v>21</v>
@@ -6451,25 +6473,25 @@
         <v>21</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH42" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>139</v>
+        <v>21</v>
       </c>
       <c r="AK42" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>21</v>
@@ -6483,14 +6505,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>253</v>
+        <v>154</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6503,26 +6525,24 @@
         <v>21</v>
       </c>
       <c r="I43" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s" s="2">
-        <v>89</v>
+        <v>21</v>
       </c>
       <c r="K43" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="O43" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>157</v>
+      </c>
+      <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
         <v>21</v>
       </c>
@@ -6570,7 +6590,7 @@
         <v>21</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>79</v>
@@ -6588,7 +6608,7 @@
         <v>21</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>131</v>
+        <v>253</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>21</v>
@@ -6602,42 +6622,46 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>21</v>
+        <v>259</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="H44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="I44" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="J44" t="s" s="2">
-        <v>21</v>
+        <v>89</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>349</v>
+        <v>133</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>350</v>
+        <v>260</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>351</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
+        <v>261</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="O44" t="s" s="2">
+        <v>158</v>
+      </c>
       <c r="P44" t="s" s="2">
         <v>21</v>
       </c>
@@ -6685,25 +6709,25 @@
         <v>21</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>348</v>
+        <v>262</v>
       </c>
       <c r="AG44" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AH44" t="s" s="2">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="AI44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>139</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>352</v>
+        <v>131</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>21</v>
@@ -6717,10 +6741,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6728,7 +6752,7 @@
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="G45" t="s" s="2">
         <v>88</v>
@@ -6743,13 +6767,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>181</v>
+        <v>355</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6776,13 +6800,13 @@
         <v>21</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>184</v>
+        <v>21</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>356</v>
+        <v>21</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>357</v>
+        <v>21</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>21</v>
@@ -6800,10 +6824,10 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG45" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AH45" t="s" s="2">
         <v>88</v>
@@ -6818,24 +6842,24 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>288</v>
+        <v>358</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>358</v>
+        <v>21</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>359</v>
+        <v>21</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6846,7 +6870,7 @@
         <v>79</v>
       </c>
       <c r="G46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H46" t="s" s="2">
         <v>21</v>
@@ -6858,13 +6882,13 @@
         <v>21</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="L46" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M46" t="s" s="2">
         <v>361</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>362</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6891,14 +6915,14 @@
         <v>21</v>
       </c>
       <c r="X46" t="s" s="2">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="Y46" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="Z46" t="s" s="2">
         <v>363</v>
       </c>
-      <c r="Z46" t="s" s="2">
-        <v>364</v>
-      </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
       </c>
@@ -6915,13 +6939,13 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AH46" t="s" s="2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="AI46" t="s" s="2">
         <v>21</v>
@@ -6933,24 +6957,24 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
+        <v>294</v>
+      </c>
+      <c r="AM46" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN46" t="s" s="2">
+        <v>364</v>
+      </c>
+      <c r="AO46" t="s" s="2">
         <v>365</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>366</v>
-      </c>
-      <c r="AO46" t="s" s="2">
-        <v>21</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6973,13 +6997,13 @@
         <v>21</v>
       </c>
       <c r="K47" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="L47" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M47" t="s" s="2">
         <v>368</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>369</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>370</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7006,13 +7030,13 @@
         <v>21</v>
       </c>
       <c r="X47" t="s" s="2">
-        <v>21</v>
+        <v>190</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>21</v>
+        <v>369</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>21</v>
+        <v>370</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7030,7 +7054,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7069,14 +7093,14 @@
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>374</v>
+        <v>21</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>79</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>21</v>
@@ -7088,17 +7112,15 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="L48" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="L48" t="s" s="2">
+      <c r="M48" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="M48" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="N48" t="s" s="2">
-        <v>378</v>
-      </c>
+      <c r="N48" s="2"/>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>21</v>
@@ -7165,13 +7187,13 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>21</v>
+        <v>378</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7179,14 +7201,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>21</v>
+        <v>380</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7264,7 +7286,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7294,8 +7316,125 @@
         <v>21</v>
       </c>
     </row>
+    <row r="50" hidden="true">
+      <c r="A50" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="B50" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="C50" s="2"/>
+      <c r="D50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="E50" s="2"/>
+      <c r="F50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="I50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="K50" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="L50" t="s" s="2">
+        <v>388</v>
+      </c>
+      <c r="M50" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="N50" t="s" s="2">
+        <v>390</v>
+      </c>
+      <c r="O50" s="2"/>
+      <c r="P50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q50" s="2"/>
+      <c r="R50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF50" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="AG50" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH50" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AI50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AJ50" t="s" s="2">
+        <v>100</v>
+      </c>
+      <c r="AK50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AL50" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AM50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AN50" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AO50" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AO49">
+  <autoFilter ref="A1:AO50">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7305,7 +7444,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI48">
+  <conditionalFormatting sqref="A2:AI49">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteAbgabe.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="392">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1871" uniqueCount="393">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:28:16+00:00</t>
+    <t>2026-05-27T13:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -89,7 +89,7 @@
   <si>
     <t>Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
 In der durchgeführten Abgabe können Abweichungen hinsichtlich des Medikaments und dessen Dosierung dokumentiert werden.
-Sofern eine zugehörige geplante Abgabe vorliegt, muss diese referenziert werden. Eine mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige geplante Abgabe, ersichtlich.</t>
+Sofern eine zugehörige geplante Abgabe vorliegt, muss diese mit dem zugehörigen Planeintrag referenziert werden. Eine mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige geplante Abgabe, ersichtlich.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -714,7 +714,7 @@
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-patient)
 </t>
   </si>
   <si>
@@ -868,7 +868,7 @@
     <t>MedicationDispense.performer.actor</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
@@ -905,11 +905,14 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
+    <t>2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(MedicationRequest|4.0.1)
 </t>
   </si>
   <si>
-    <t>Verpflichtende Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert.</t>
+    <t>Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert bzw. Planeintrag (MedicationRequest).</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
@@ -1587,7 +1590,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="205.50390625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="195.8359375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -5135,7 +5138,7 @@
         <v>79</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>88</v>
+        <v>282</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>89</v>
@@ -5147,16 +5150,16 @@
         <v>21</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5221,27 +5224,27 @@
         <v>100</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5267,10 +5270,10 @@
         <v>187</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5300,10 +5303,10 @@
         <v>190</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>21</v>
@@ -5321,7 +5324,7 @@
         <v>21</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>79</v>
@@ -5339,24 +5342,24 @@
         <v>21</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5379,13 +5382,13 @@
         <v>21</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -5436,7 +5439,7 @@
         <v>21</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -5454,24 +5457,24 @@
         <v>21</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="AO33" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5494,13 +5497,13 @@
         <v>21</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5551,7 +5554,7 @@
         <v>21</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -5569,7 +5572,7 @@
         <v>21</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>21</v>
@@ -5578,15 +5581,15 @@
         <v>21</v>
       </c>
       <c r="AO34" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5609,13 +5612,13 @@
         <v>89</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -5666,7 +5669,7 @@
         <v>21</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -5684,24 +5687,24 @@
         <v>21</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO35" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5724,13 +5727,13 @@
         <v>21</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -5781,7 +5784,7 @@
         <v>21</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -5796,27 +5799,27 @@
         <v>100</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5842,10 +5845,10 @@
         <v>277</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5896,7 +5899,7 @@
         <v>21</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>79</v>
@@ -5914,24 +5917,24 @@
         <v>21</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5954,13 +5957,13 @@
         <v>21</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6011,7 +6014,7 @@
         <v>21</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>79</v>
@@ -6029,13 +6032,13 @@
         <v>21</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>21</v>
@@ -6043,10 +6046,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6069,13 +6072,13 @@
         <v>21</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6126,7 +6129,7 @@
         <v>21</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>79</v>
@@ -6141,10 +6144,10 @@
         <v>100</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>21</v>
@@ -6153,15 +6156,15 @@
         <v>21</v>
       </c>
       <c r="AO39" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6184,16 +6187,16 @@
         <v>21</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6243,7 +6246,7 @@
         <v>21</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>79</v>
@@ -6261,7 +6264,7 @@
         <v>21</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>21</v>
@@ -6275,10 +6278,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6304,10 +6307,10 @@
         <v>243</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6358,7 +6361,7 @@
         <v>21</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>79</v>
@@ -6376,13 +6379,13 @@
         <v>21</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>21</v>
@@ -6390,10 +6393,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6505,10 +6508,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6622,10 +6625,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6741,10 +6744,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6767,13 +6770,13 @@
         <v>21</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6824,7 +6827,7 @@
         <v>21</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>88</v>
@@ -6842,7 +6845,7 @@
         <v>21</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>21</v>
@@ -6856,10 +6859,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6885,10 +6888,10 @@
         <v>187</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6918,10 +6921,10 @@
         <v>190</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>21</v>
@@ -6939,7 +6942,7 @@
         <v>21</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>79</v>
@@ -6957,24 +6960,24 @@
         <v>21</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7000,10 +7003,10 @@
         <v>187</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" s="2"/>
@@ -7033,10 +7036,10 @@
         <v>190</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>21</v>
@@ -7054,7 +7057,7 @@
         <v>21</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>79</v>
@@ -7072,13 +7075,13 @@
         <v>21</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>21</v>
@@ -7086,10 +7089,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7112,13 +7115,13 @@
         <v>21</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7169,7 +7172,7 @@
         <v>21</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>79</v>
@@ -7187,13 +7190,13 @@
         <v>21</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>21</v>
@@ -7201,14 +7204,14 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
@@ -7227,16 +7230,16 @@
         <v>21</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7286,7 +7289,7 @@
         <v>21</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>79</v>
@@ -7304,7 +7307,7 @@
         <v>21</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>21</v>
@@ -7318,10 +7321,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7344,16 +7347,16 @@
         <v>21</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7403,7 +7406,7 @@
         <v>21</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>79</v>
@@ -7421,7 +7424,7 @@
         <v>21</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>21</v>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteAbgabe.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medikationdispense-durchgefuehrteAbgabe.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:46:49+00:00</t>
+    <t>2026-05-28T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
